--- a/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixed Horizon Parameters'!$A$1:$G$277</definedName>
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2433,6 +2433,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>39</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>StorageLevelStart</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>39</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OperationalLifeStorage</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>40</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>StorageLevelStart</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>40</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OperationalLifeStorage</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G277"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2445,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ77"/>
+  <dimension ref="A1:AJ81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -8579,6 +8683,286 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>39</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="J78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="K78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="L78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="M78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="N78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="O78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="P78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="R78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="S78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="T78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="U78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="V78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="W78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="X78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>32777.77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>39</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ResidualStorageCapacity</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>40</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="J80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="K80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="L80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="M80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="N80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="O80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="P80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="R80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="S80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="T80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="U80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="V80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="W80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="X80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>32777.77</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>32777.77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>40</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ResidualStorageCapacity</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AO161"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8591,7 +8975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14124,8 +14508,517 @@
         <v>1</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PWRBDSCHLXX</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PWRBDSCHLXX</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PWRBDSCHLXX</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PWRBDSCHLXX</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Chile, region XX</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BDSCHLXX01</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Chile, region XX</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PWRBDSPERXX</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PWRBDSPERXX</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>2</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PWRBDSPERXX</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PWRBDSPERXX</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator, non-renewable) Peru, region XX</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BDSPERXX01</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Short duration storage non-renewable Peru, region XX</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83cf53e23258b582a307689f9bad4776">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8e6c764710efd91b3147b7c3b8958216" ns2:_="" ns3:_="">
+    <xsd:import namespace="7db9c71a-8f0f-4486-8c92-6242e053eab7"/>
+    <xsd:import namespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7db9c71a-8f0f-4486-8c92-6242e053eab7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{79606235-ded0-4d00-a81d-9caf851eecac}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="8ae01698-3168-4e7f-b9e7-0ddc1c80de73">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7db9c71a-8f0f-4486-8c92-6242e053eab7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA37AF7-93F5-4DEB-91F5-61F2F6444ABC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC49EE81-BBA8-4CF5-A619-13DF2DF0AFF1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58CEBF89-BC66-477D-B7AA-899CDD64854C}"/>
 </file>
--- a/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixed Horizon Parameters'!$A$1:$G$277</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,13 +36,25 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,13 +69,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14802,223 +14822,226 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48F53D8446FB4EB61FD3AFE2640F25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83cf53e23258b582a307689f9bad4776">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7db9c71a-8f0f-4486-8c92-6242e053eab7" xmlns:ns3="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8e6c764710efd91b3147b7c3b8958216" ns2:_="" ns3:_="">
-    <xsd:import namespace="7db9c71a-8f0f-4486-8c92-6242e053eab7"/>
-    <xsd:import namespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7db9c71a-8f0f-4486-8c92-6242e053eab7" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{79606235-ded0-4d00-a81d-9caf851eecac}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="8ae01698-3168-4e7f-b9e7-0ddc1c80de73">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7db9c71a-8f0f-4486-8c92-6242e053eab7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8ae01698-3168-4e7f-b9e7-0ddc1c80de73" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA37AF7-93F5-4DEB-91F5-61F2F6444ABC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC49EE81-BBA8-4CF5-A619-13DF2DF0AFF1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58CEBF89-BC66-477D-B7AA-899CDD64854C}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Fuentes de los datos de este libro. Las fuentes SUBRAYADAS son supuestos propios del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Hoja</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Tecnologias</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Anios</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Fixed Horizon Parameters</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>LDS*, SDS*, BDS* (almacenamiento de larga duración, corta duración y baterías)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>StorageLevelStart, OperationalLifeStorage</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Nivel inicial de almacenamiento (0) y vida útil (larga duración 60 años, corta duración y baterías 30 años). Las baterías (BDS, solo Chile y Perú) copian los valores de corta duración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>LDS* (almacenamiento de larga duración, 19 países)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2023-2050</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>NREL ATB 2024 (Annual Technology Baseline del National Renewable Energy Laboratory, EE. UU.)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Componente de energía del costo del almacenamiento: 20 833.33 millones de USD por PJ, equivalente a 75 USD por kWh, constante; cargado en la versión anterior del modelo ReLAC (agosto 2025). OSeMOSYS Global traía 52 694 millones de USD por PJ (≈ 190 USD/kWh), valor que no se usa. El componente de potencia está en la hoja Secondary Techs de A-O_Parametrization (PWRLDS*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>SDS* (almacenamiento de corta duración, 19 países) y BDS* (baterías, Chile y Perú)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2023-2050</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>NREL ATB 2024 (Annual Technology Baseline del National Renewable Energy Laboratory, EE. UU.)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Componente de energía del costo: 32 777.77 millones de USD por PJ, equivalente a 118 USD por kWh, constante; cargado en la versión anterior del modelo ReLAC (agosto 2025). OSeMOSYS Global traía 42 051 millones de USD por PJ (≈ 151 USD/kWh), valor que no se usa. El componente de potencia (944 USD/kW) está en la hoja Secondary Techs de A-O_Parametrization (PWRSDS*, PWRBDS*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>LDS*, SDS* (almacenamiento existente)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ResidualStorageCapacity</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2023-2050</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Capacidad de almacenamiento existente; solo Argentina, Bolivia, Brasil, Haití y México tienen valores distintos de cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TechnologyStorage</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>PWRLDS* / PWRSDS* / PWRBDS* ↔ LDS* / SDS* / BDS* (vínculo entre la planta de almacenamiento y su depósito)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage, TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Indica qué tecnología carga (modo 1) y descarga (modo 2) cada depósito de almacenamiento.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+          <t>Vida útil: NREL Annual Technology Baseline, según la tabla de valores por defecto de OSeMOSYS Global; nivel inicial: supuesto interno de OSeMOSYS Global</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Nivel inicial de almacenamiento (0) y vida útil (larga duración 60 años, corta duración y baterías 30 años). Las baterías (BDS, solo Chile y Perú) copian los valores de corta duración.</t>
+          <t>Vida útil de 60 años para almacenamiento de larga duración y 30 para corta duración y baterías (tabla por defecto de OSeMOSYS Global, basada en el NREL ATB). Nivel inicial de almacenamiento 0 (valor por defecto). Las baterías (BDS, solo Chile y Perú) copian los valores de corta duración.</t>
         </is>
       </c>
     </row>
@@ -14997,12 +14997,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+          <t>DOE / Sandia – Global Energy Storage Database (GESDB), a través de OSeMOSYS Global</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Capacidad de almacenamiento existente; solo Argentina, Bolivia, Brasil, Haití y México tienen valores distintos de cero.</t>
+          <t>Capacidad de almacenamiento existente por país según los proyectos ya comisionados de la GESDB, clasificados por OSeMOSYS Global en larga duración (bombeo hidráulico, aire comprimido, hidrógeno) y corta duración (baterías, volantes de inercia, térmicos); MWh convertidos a PJ. Solo Argentina, Bolivia, Brasil, Haití y México tienen valores distintos de cero.</t>
         </is>
       </c>
     </row>
@@ -15029,12 +15029,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
+          <t>Estructura del modelo definida por OSeMOSYS Global (sin fuente externa)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Indica qué tecnología carga (modo 1) y descarga (modo 2) cada depósito de almacenamiento.</t>
+          <t>Indica qué tecnología carga (modo 1) y descarga (modo 2) cada depósito de almacenamiento; es parte de la estructura del modelo, no un dato.</t>
         </is>
       </c>
     </row>

--- a/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fuentes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixed Horizon Parameters'!$A$1:$G$277</definedName>
@@ -14842,7 +14842,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Fuentes de los datos de este libro. Las fuentes SUBRAYADAS son supuestos propios del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
+          <t>Fuentes de los datos de este libro. Las fuentes marcadas como 'Supuesto propio' son estimaciones internas del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
         </is>
       </c>
     </row>

--- a/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/inputs/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -14864,7 +14864,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Anios</t>
+          <t>Años</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
